--- a/data/trans_bre/P1805_2016_2023-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P1805_2016_2023-Habitat-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,21</t>
+          <t>-0,12; 3,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 1,61</t>
+          <t>-1,86; 1,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,58; 446,22</t>
+          <t>-22,44; 438,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-44,96; 110,61</t>
+          <t>-46,96; 94,4</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,9</t>
+          <t>1,26</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>105,8%</t>
+          <t>54,9%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,25</t>
+          <t>0,37; 3,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,45</t>
+          <t>-0,24; 2,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,39; 287,07</t>
+          <t>10,56; 281,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,84; 344,97</t>
+          <t>-9,48; 176,09</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>1,56</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>42,94%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 3,15</t>
+          <t>0,12; 3,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 3,04</t>
+          <t>-0,84; 3,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 382,49</t>
+          <t>-2,79; 367,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-53,21; 113,09</t>
+          <t>-20,89; 162,67</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-0,19</t>
+          <t>0,49</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,84%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,37</t>
+          <t>0,71; 4,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 1,83</t>
+          <t>-1,59; 2,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,14; 211,47</t>
+          <t>17,77; 219,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-38,61; 51,3</t>
+          <t>-26,85; 61,5</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>26,93%</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,8</t>
+          <t>1,17; 2,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,86</t>
+          <t>-0,15; 1,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49,87; 189,32</t>
+          <t>54,0; 184,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 74,69</t>
+          <t>-4,4; 65,6</t>
         </is>
       </c>
     </row>
